--- a/ig/xdsdocuments/StructureDefinition-medcom-contained-documentreference.xlsx
+++ b/ig/xdsdocuments/StructureDefinition-medcom-contained-documentreference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-trial-use-1</t>
+    <t>1.0.0-trial-use-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T09:36:40+00:00</t>
+    <t>2026-06-17T08:46:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
